--- a/output/graficos_regionales/plot_regional_serie_i_ingr_m_2023_biobio.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_m_2023_biobio.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:38</t>
+    <t xml:space="preserve">2026-10-05 01:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -726,7 +726,7 @@
         <v>714882.5</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>804762.62</v>
+        <v>804762.63</v>
       </c>
     </row>
     <row r="5">
@@ -737,7 +737,7 @@
         <v>716045.5</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>799364.12</v>
+        <v>799364.13</v>
       </c>
     </row>
     <row r="6">
@@ -836,7 +836,7 @@
         <v>747532.81</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>826816.62</v>
+        <v>826816.63</v>
       </c>
     </row>
     <row r="15">
@@ -913,7 +913,7 @@
         <v>767815.56</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>849932.62</v>
+        <v>849932.63</v>
       </c>
     </row>
     <row r="22">
@@ -943,7 +943,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>785923.12</v>
+        <v>785923.13</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>864071.75</v>
@@ -1001,7 +1001,7 @@
         <v>800610.25</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>885489.12</v>
+        <v>885489.13</v>
       </c>
     </row>
     <row r="30">
@@ -1012,7 +1012,7 @@
         <v>797740.88</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>873830.12</v>
+        <v>873830.13</v>
       </c>
     </row>
     <row r="31">
@@ -1166,7 +1166,7 @@
         <v>872474.81</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>953641.12</v>
+        <v>953641.13</v>
       </c>
     </row>
     <row r="45">
@@ -1185,7 +1185,7 @@
         <v>47</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>903566.12</v>
+        <v>903566.13</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>990310.88</v>
@@ -1207,7 +1207,7 @@
         <v>49</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>879601.12</v>
+        <v>879601.13</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>964866.69</v>
@@ -1229,7 +1229,7 @@
         <v>51</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>907773.62</v>
+        <v>907773.63</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>990892.69</v>
@@ -1240,7 +1240,7 @@
         <v>52</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>896310.62</v>
+        <v>896310.63</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>984727.69</v>
@@ -1287,7 +1287,7 @@
         <v>965013.75</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>1048559.62</v>
+        <v>1048559.63</v>
       </c>
     </row>
     <row r="56">
@@ -1298,7 +1298,7 @@
         <v>967221.25</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1059287.62</v>
+        <v>1059287.63</v>
       </c>
     </row>
     <row r="57">
@@ -1342,7 +1342,7 @@
         <v>1009370.19</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>1093564.62</v>
+        <v>1093564.63</v>
       </c>
     </row>
     <row r="61">
@@ -1364,7 +1364,7 @@
         <v>1050733</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>1145616.62</v>
+        <v>1145616.63</v>
       </c>
     </row>
     <row r="63">
@@ -1372,7 +1372,7 @@
         <v>64</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>1037596.62</v>
+        <v>1037596.63</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>1133168.75</v>
@@ -1419,7 +1419,7 @@
         <v>1091112.88</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>1184430.62</v>
+        <v>1184430.63</v>
       </c>
     </row>
     <row r="68">
@@ -1427,7 +1427,7 @@
         <v>69</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>1086956.62</v>
+        <v>1086956.63</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>1185328.75</v>
@@ -1460,7 +1460,7 @@
         <v>72</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>1101258.12</v>
+        <v>1101258.13</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>1202545</v>
@@ -1493,7 +1493,7 @@
         <v>75</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>1116787.12</v>
+        <v>1116787.13</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>1224566.38</v>
@@ -1504,7 +1504,7 @@
         <v>76</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>1101482.12</v>
+        <v>1101482.13</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>1214165.25</v>
@@ -1515,10 +1515,10 @@
         <v>77</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>1119193.12</v>
+        <v>1119193.13</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>1240434.12</v>
+        <v>1240434.13</v>
       </c>
     </row>
     <row r="77">
@@ -1526,7 +1526,7 @@
         <v>78</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>1138887.62</v>
+        <v>1138887.63</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>1250444</v>
@@ -1551,7 +1551,7 @@
         <v>1133808.75</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>1253268.12</v>
+        <v>1253268.13</v>
       </c>
     </row>
     <row r="80">
@@ -1562,7 +1562,7 @@
         <v>1155541.38</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>1274861.62</v>
+        <v>1274861.63</v>
       </c>
     </row>
     <row r="81">
@@ -1584,7 +1584,7 @@
         <v>1203429</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>1327655.12</v>
+        <v>1327655.13</v>
       </c>
     </row>
     <row r="83">
@@ -1614,7 +1614,7 @@
         <v>86</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>1235772.62</v>
+        <v>1235772.63</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>1353554.88</v>
